--- a/Luban/Config/Datas/Levels/L10/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L10/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L10 W1/25; N=40; EHP=235.840000; normal:17x20,normal:18x20</t>
+          <t>L10 W1/25; N=40; EHP=508.295087; normal:17x20,normal:18x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L10 W2/25; N=46; EHP=283.990274; normal:17x23,normal:18x23</t>
+          <t>L10 W2/25; N=46; EHP=612.071153; normal:17x23,normal:18x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3464136,3464673,3464019,3464136,3464673,3464091,3464136,3464673,3464099,3464136,3464673,3464099,3464136,3464673,3464107,3464136,3464673,3464115,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464136,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144</t>
+          <t>3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464673,3464136,3464136,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464144,3464136,3464136,3464136,3464136,3464136,3464136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L10 W3/25; N=52; EHP=355.156173; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x16,normal:18x16,swarm:84x14</t>
+          <t>L10 W3/25; N=52; EHP=823.122758; normal:17x22,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3466136,3466673,3466019,3466136,3466673,3466019,3466136,3466673,3466091,3466136,3466673,3466099,3466136,3466673,3466107,3466136,3466673,3466107,3466136,3466673,3466115,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144</t>
+          <t>3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466673,3466136,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144,3466144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L10 W4/25; N=58; EHP=456.151115; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x17,normal:18x18,swarm:84x16</t>
+          <t>L10 W4/25; N=58; EHP=1061.082713; normal:17x17,normal:18x25,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3468136,3468673,3468019,3468668,3468136,3468673,3468091,3468668,3468136,3468673,3468091,3468668,3468136,3468673,3468099,3468868,3468136,3468673,3468107,3468868,3468136,3468673,3468107,3468868,3468136,3468673,3468115,3468988,3468136,3468673,3468115,3468988,3468136,3468673,3468988,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468144,3468673,3468144,3468673,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144</t>
+          <t>3468136,3468019,3468019,3468668,3468136,3468091,3468091,3468668,3468136,3468091,3468091,3468668,3468136,3468099,3468099,3468868,3468136,3468107,3468107,3468868,3468136,3468107,3468107,3468868,3468136,3468115,3468115,3468988,3468136,3468115,3468115,3468988,3468136,3468673,3468988,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468136,3468673,3468144,3468673,3468144,3468673,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144,3468144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L10 W5/25; N=64; EHP=866.931237; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x15,normal:18x15,medium:83x3,swarm:84x17,medium:108x3,medium:123x3</t>
+          <t>L10 W5/25; N=64; EHP=1893.390492; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x3,normal:17x15,normal:18x15,swarm:84x9 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3470136,3470673,3470242,3470019,3470668,3470136,3470673,3470242,3470091,3470668,3470136,3470673,3470466,3470091,3470668,3470136,3470673,3470466,3470099,3470868,3470136,3470673,3470514,3470099,3470868,3470136,3470673,3470514,3470107,3470868,3470136,3470673,3470786,3470115,3470988,3470136,3470673,3470786,3470115,3470988,3470136,3470673,3470988,3470136,3470673,3470988,3470136,3470673,3470136,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470144,3470144,3470144,3470144,3470144</t>
+          <t>3470136,3470019,3470242,3470019,3470668,3470136,3470091,3470242,3470091,3470668,3470136,3470091,3470466,3470091,3470668,3470136,3470099,3470466,3470099,3470868,3470136,3470099,3470514,3470099,3470868,3470136,3470107,3470514,3470107,3470868,3470136,3470115,3470786,3470115,3470988,3470136,3470115,3470786,3470115,3470988,3470136,3470673,3470988,3470136,3470673,3470988,3470136,3470673,3470136,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470673,3470144,3470144,3470144,3470144,3470144,3470144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L10 W6/25; N=70; EHP=885.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x3,swarm:84x19,fast:98x2,medium:108x3,medium:123x4</t>
+          <t>L10 W6/25; N=70; EHP=1930.966056; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x2,medium:83x3,medium:108x3,medium:123x4,normal:17x12,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3472136,3472673,3472242,3472019,3472668,3472136,3472673,3472242,3472019,3472668,3472136,3472673,3472466,3472091,3472668,3472136,3472673,3472466,3472099,3472668,3472136,3472673,3472514,3472099,3472868,3472136,3472673,3472514,3472107,3472868,3472136,3472673,3472786,3472107,3472868,3472136,3472673,3472786,3472115,3472868,3472136,3472673,3472786,3472115,3472988,3472136,3472673,3472988,3472136,3472673,3472988,3472136,3472673,3472136,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472144,3472144,3472144,3472144</t>
+          <t>3472136,3472019,3472242,3472019,3472668,3472136,3472019,3472242,3472019,3472668,3472136,3472091,3472466,3472091,3472668,3472136,3472099,3472466,3472099,3472668,3472136,3472099,3472514,3472099,3472868,3472136,3472107,3472514,3472107,3472868,3472136,3472107,3472786,3472107,3472868,3472136,3472115,3472786,3472115,3472868,3472136,3472115,3472786,3472115,3472988,3472136,3472673,3472988,3472136,3472673,3472988,3472136,3472673,3472136,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472673,3472144,3472144,3472144,3472144,3472144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L10 W7/25; N=76; EHP=1006.244378; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x21,fast:98x3,medium:108x4,medium:123x3</t>
+          <t>L10 W7/25; N=76; EHP=2196.575688; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x3,normal:17x13,normal:18x13,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3474136,3474673,3474242,3474019,3474668,3474136,3474673,3474242,3474019,3474668,3474136,3474673,3474466,3474091,3474668,3474136,3474673,3474466,3474091,3474668,3474136,3474673,3474466,3474099,3474868,3474136,3474673,3474514,3474099,3474868,3474136,3474673,3474514,3474107,3474868,3474136,3474673,3474786,3474107,3474868,3474136,3474673,3474786,3474115,3474988,3474136,3474673,3474115,3474988,3474136,3474673,3474988,3474136,3474673,3474988,3474136,3474673,3474136,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474144,3474144,3474144,3474144,3474144,3474144</t>
+          <t>3474136,3474019,3474242,3474019,3474668,3474136,3474019,3474242,3474019,3474668,3474136,3474091,3474466,3474091,3474668,3474136,3474091,3474466,3474091,3474668,3474136,3474099,3474466,3474099,3474868,3474136,3474099,3474514,3474099,3474868,3474136,3474107,3474514,3474107,3474868,3474136,3474107,3474786,3474107,3474868,3474136,3474115,3474786,3474115,3474988,3474136,3474115,3474115,3474988,3474136,3474673,3474988,3474136,3474673,3474988,3474136,3474673,3474136,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474673,3474144,3474144,3474144,3474144,3474144,3474144,3474144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L10 W8/25; N=82; EHP=1296.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L10 W8/25; N=82; EHP=2830.034526; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3476136,3476673,3476242,3476019,3476668,3476136,3476673,3476242,3476019,3476668,3476136,3476673,3476242,3476019,3476668,3476136,3476673,3476466,3476091,3476668,3476136,3476673,3476466,3476091,3476868,3476136,3476673,3476514,3476099,3476868,3476136,3476673,3476514,3476099,3476868,3476136,3476673,3476514,3476107,3476868,3476136,3476673,3476786,3476107,3476988,3476136,3476673,3476786,3476115,3476988,3476136,3476673,3476115,3476988,3476136,3476673,3476988,3476136,3476673,3476988,3476136,3476673,3476136,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476144,3476144,3476144,3476144,3476144</t>
+          <t>3476136,3476019,3476242,3476019,3476668,3476136,3476019,3476242,3476019,3476668,3476136,3476019,3476242,3476019,3476668,3476136,3476091,3476466,3476091,3476668,3476136,3476091,3476466,3476091,3476868,3476136,3476099,3476514,3476099,3476868,3476136,3476099,3476514,3476099,3476868,3476136,3476107,3476514,3476107,3476868,3476136,3476107,3476786,3476107,3476988,3476136,3476115,3476786,3476115,3476988,3476136,3476115,3476115,3476988,3476136,3476673,3476988,3476136,3476673,3476988,3476136,3476673,3476136,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476673,3476144,3476144,3476144,3476144,3476144,3476144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L10 W9/25; N=88; EHP=1654.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L10 W9/25; N=88; EHP=3613.111244; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x5,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3478136,3478673,3478242,3478019,3478668,3478136,3478673,3478242,3478019,3478668,3478136,3478673,3478242,3478091,3478668,3478136,3478673,3478466,3478091,3478668,3478136,3478673,3478466,3478099,3478668,3478136,3478673,3478466,3478099,3478868,3478136,3478673,3478514,3478107,3478868,3478136,3478673,3478514,3478107,3478868,3478136,3478673,3478786,3478107,3478868,3478136,3478673,3478786,3478115,3478868,3478136,3478673,3478786,3478115,3478988,3478136,3478673,3478988,3478136,3478673,3478988,3478136,3478673,3478988,3478136,3478673,3478136,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478144,3478144,3478144,3478144,3478144</t>
+          <t>3478136,3478019,3478242,3478019,3478668,3478136,3478019,3478242,3478019,3478668,3478136,3478091,3478242,3478091,3478668,3478136,3478091,3478466,3478091,3478668,3478136,3478099,3478466,3478099,3478668,3478136,3478099,3478466,3478099,3478868,3478136,3478107,3478514,3478107,3478868,3478136,3478107,3478514,3478107,3478868,3478136,3478107,3478786,3478107,3478868,3478136,3478115,3478786,3478115,3478868,3478136,3478115,3478786,3478115,3478988,3478136,3478673,3478988,3478136,3478673,3478988,3478136,3478673,3478988,3478136,3478673,3478136,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478673,3478144,3478144,3478144,3478144,3478144,3478144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L10 W10/25; N=94; EHP=3053.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x3,fast:64x2,medium:83x5,swarm:84x26,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L10 W10/25; N=94; EHP=6663.185526; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3480136,3480673,3480242,3480019,3480668,3480253,3480136,3480673,3480242,3480019,3480668,3480325,3480136,3480673,3480242,3480091,3480668,3480565,3480136,3480673,3480466,3480091,3480668,3480645,3480136,3480673,3480466,3480091,3480668,3480645,3480136,3480673,3480466,3480099,3480868,3480693,3480136,3480673,3480514,3480099,3480868,3480693,3480136,3480673,3480514,3480107,3480868,3480709,3480136,3480673,3480514,3480107,3480868,3480709,3480136,3480673,3480786,3480115,3480868,3481021,3480136,3480673,3480786,3480115,3480988,3480136,3480673,3480786,3480115,3480988,3480144,3480673,3480988,3480144,3480673,3480988,3480144,3480673,3480988,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480673,3480673,3480673,3480673,3480673</t>
+          <t>3480136,3480019,3480242,3480019,3480668,3480253,3480136,3480019,3480242,3480019,3480668,3480325,3480136,3480091,3480242,3480091,3480668,3480565,3480136,3480091,3480466,3480091,3480668,3480645,3480136,3480091,3480466,3480091,3480668,3480645,3480136,3480099,3480466,3480099,3480868,3480693,3480136,3480099,3480514,3480099,3480868,3480693,3480136,3480107,3480514,3480107,3480868,3480709,3480136,3480107,3480514,3480107,3480868,3480709,3480136,3480115,3480786,3480115,3480868,3481021,3480136,3480115,3480786,3480115,3480988,3480136,3480115,3480786,3480115,3480988,3480144,3480673,3480988,3480144,3480673,3480988,3480144,3480673,3480988,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480144,3480673,3480673,3480673,3480673,3480673,3480673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L10 W11/25; N=100; EHP=3115.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x12,normal:18x11,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x28,heavy:86x2,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L10 W11/25; N=100; EHP=6790.857977; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x12,normal:18x11,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3482136,3482673,3482242,3482019,3482668,3482253,3482136,3482673,3482242,3482019,3482668,3482253,3482136,3482673,3482242,3482019,3482668,3482325,3482136,3482673,3482466,3482091,3482668,3482565,3482136,3482673,3482466,3482091,3482668,3482645,3482136,3482673,3482466,3482099,3482868,3482645,3482136,3482673,3482514,3482099,3482868,3482693,3482136,3482673,3482514,3482099,3482868,3482693,3482136,3482673,3482514,3482107,3482868,3482709,3482136,3482673,3482786,3482107,3482868,3483021,3482136,3482673,3482786,3482115,3482988,3482136,3482673,3482786,3482115,3482988,3482136,3482673,3482115,3482988,3482144,3482673,3482988,3482144,3482673,3482988,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482673,3482673</t>
+          <t>3482136,3482019,3482242,3482019,3482668,3482253,3482136,3482019,3482242,3482019,3482668,3482253,3482136,3482019,3482242,3482019,3482668,3482325,3482136,3482091,3482466,3482091,3482668,3482565,3482136,3482091,3482466,3482091,3482668,3482645,3482136,3482099,3482466,3482099,3482868,3482645,3482136,3482099,3482514,3482099,3482868,3482693,3482136,3482099,3482514,3482099,3482868,3482693,3482136,3482107,3482514,3482107,3482868,3482709,3482136,3482107,3482786,3482107,3482868,3483021,3482136,3482115,3482786,3482115,3482988,3482136,3482115,3482786,3482115,3482988,3482136,3482115,3482115,3482988,3482144,3482673,3482988,3482144,3482673,3482988,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482144,3482673,3482673,3482673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L10 W12/25; N=106; EHP=3224.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x3,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x29,heavy:86x2,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L10 W12/25; N=106; EHP=7031.108141; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x2,heavy:40x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x14,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3484136,3484673,3484242,3484019,3484668,3484253,3484136,3484673,3484242,3484019,3484668,3484253,3484136,3484673,3484242,3484019,3484668,3484325,3484136,3484673,3484466,3484091,3484668,3484325,3484136,3484673,3484466,3484091,3484668,3484565,3484136,3484673,3484466,3484099,3484868,3484645,3484136,3484673,3484514,3484099,3484868,3484693,3484136,3484673,3484514,3484099,3484868,3484693,3484136,3484673,3484514,3484107,3484868,3484709,3484136,3484673,3484514,3484107,3484868,3485021,3484136,3484673,3484786,3484107,3484868,3485021,3484136,3484673,3484786,3484115,3484988,3484136,3484673,3484786,3484115,3484988,3484136,3484673,3484988,3484144,3484673,3484988,3484144,3484673,3484988,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484673,3484673,3484673</t>
+          <t>3484136,3484019,3484242,3484019,3484668,3484253,3484136,3484019,3484242,3484019,3484668,3484253,3484136,3484019,3484242,3484019,3484668,3484325,3484136,3484091,3484466,3484091,3484668,3484325,3484136,3484091,3484466,3484091,3484668,3484565,3484136,3484099,3484466,3484099,3484868,3484645,3484136,3484099,3484514,3484099,3484868,3484693,3484136,3484099,3484514,3484099,3484868,3484693,3484136,3484107,3484514,3484107,3484868,3484709,3484136,3484107,3484514,3484107,3484868,3485021,3484136,3484107,3484786,3484107,3484868,3485021,3484136,3484115,3484786,3484115,3484988,3484136,3484115,3484786,3484115,3484988,3484136,3484673,3484988,3484144,3484673,3484988,3484144,3484673,3484988,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484144,3484673,3484673,3484673,3484673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L10 W13/25; N=112; EHP=3934.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x2</t>
+          <t>L10 W13/25; N=112; EHP=8573.422455; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x5,medium:108x6,medium:123x5,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3486136,3486673,3486242,3486019,3486668,3486253,3486136,3486673,3486242,3486019,3486668,3486253,3486136,3486673,3486242,3486019,3486668,3486325,3486136,3486673,3486242,3486091,3486668,3486325,3486136,3486673,3486466,3486091,3486668,3486565,3486136,3486673,3486466,3486091,3486668,3486565,3486136,3486673,3486466,3486099,3486868,3486645,3486136,3486673,3486514,3486099,3486868,3486693,3486136,3486673,3486514,3486107,3486868,3486709,3486136,3486673,3486514,3486107,3486868,3487021,3486136,3486673,3486786,3486107,3486868,3487021,3486136,3486673,3486786,3486115,3486988,3486136,3486673,3486786,3486115,3486988,3486136,3486673,3486786,3486115,3486988,3486144,3486673,3486988,3486144,3486673,3486988,3486144,3486673,3486988,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486673,3486673,3486673,3486673</t>
+          <t>3486136,3486019,3486242,3486019,3486668,3486253,3486136,3486019,3486242,3486019,3486668,3486253,3486136,3486019,3486242,3486019,3486668,3486325,3486136,3486091,3486242,3486091,3486668,3486325,3486136,3486091,3486466,3486091,3486668,3486565,3486136,3486091,3486466,3486091,3486668,3486565,3486136,3486099,3486466,3486099,3486868,3486645,3486136,3486099,3486514,3486099,3486868,3486693,3486136,3486107,3486514,3486107,3486868,3486709,3486136,3486107,3486514,3486107,3486868,3487021,3486136,3486107,3486786,3486107,3486868,3487021,3486136,3486115,3486786,3486115,3486988,3486136,3486115,3486786,3486115,3486988,3486136,3486115,3486786,3486115,3486988,3486144,3486673,3486988,3486144,3486673,3486988,3486144,3486673,3486988,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486144,3486673,3486673,3486673,3486673,3486673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L10 W14/25; N=118; EHP=4748.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x3,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x1,fast:98x4,medium:108x5,medium:123x6,heavy:127x2</t>
+          <t>L10 W14/25; N=118; EHP=10350.816327; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x5,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3488136,3488673,3488242,3488019,3488668,3488253,3488566,3488136,3488673,3488242,3488019,3488668,3488325,3488136,3488673,3488242,3488019,3488668,3488325,3488136,3488673,3488466,3488091,3488668,3488565,3488136,3488673,3488466,3488091,3488668,3488565,3488136,3488673,3488466,3488091,3488668,3488645,3488136,3488673,3488466,3488099,3488868,3488645,3488136,3488673,3488514,3488099,3488868,3488693,3488136,3488673,3488514,3488099,3488868,3488709,3488136,3488673,3488514,3488107,3488868,3488709,3488136,3488673,3488786,3488107,3488868,3489021,3488136,3488673,3488786,3488107,3488868,3489021,3488136,3488673,3488786,3488115,3488988,3488136,3488673,3488786,3488115,3488988,3488136,3488673,3488115,3488988,3488144,3488673,3488988,3488144,3488673,3488988,3488144,3488673,3488988,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488673,3488673,3488673,3488673</t>
+          <t>3488136,3488019,3488242,3488019,3488668,3488253,3488566,3488136,3488019,3488242,3488019,3488668,3488325,3488136,3488019,3488242,3488019,3488668,3488325,3488136,3488091,3488466,3488091,3488668,3488565,3488136,3488091,3488466,3488091,3488668,3488565,3488136,3488091,3488466,3488091,3488668,3488645,3488136,3488099,3488466,3488099,3488868,3488645,3488136,3488099,3488514,3488099,3488868,3488693,3488136,3488099,3488514,3488099,3488868,3488709,3488136,3488107,3488514,3488107,3488868,3488709,3488136,3488107,3488786,3488107,3488868,3489021,3488136,3488107,3488786,3488107,3488868,3489021,3488136,3488115,3488786,3488115,3488988,3488136,3488115,3488786,3488115,3488988,3488136,3488115,3488115,3488988,3488144,3488673,3488988,3488144,3488673,3488988,3488144,3488673,3488988,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488144,3488673,3488673,3488673,3488673,3488673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L10 W15/25; N=124; EHP=8286.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x3,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,elite:70x1,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L10 W15/25; N=124; EHP=18060.528750; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:70x1,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3490136,3490673,3490242,3490019,3490668,3490253,3490136,3490673,3490242,3490019,3490668,3490253,3490136,3490673,3490242,3490019,3490668,3490325,3490136,3490673,3490242,3490091,3490668,3490565,3490136,3490673,3490466,3490091,3490668,3490565,3490136,3490673,3490466,3490091,3490668,3490645,3490136,3490673,3490466,3490091,3490868,3490645,3490136,3490673,3490466,3490099,3490868,3490693,3490136,3490673,3490514,3490099,3490868,3490693,3490136,3490673,3490514,3490099,3490868,3490709,3490136,3490673,3490514,3490107,3490868,3490709,3490136,3490673,3490514,3490107,3490868,3491021,3490136,3490673,3490786,3490107,3490868,3491021,3490136,3490673,3490786,3490115,3490988,3490136,3490673,3490786,3490115,3490988,3490144,3490673,3490115,3490988,3490144,3490673,3490988,3490144,3490673,3490988,3490144,3490673,3490988,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490673,3490673,3490673,3490673,3490673</t>
+          <t>3490136,3490019,3490242,3490019,3490668,3490253,3490136,3490019,3490242,3490019,3490668,3490253,3490136,3490019,3490242,3490019,3490668,3490325,3490136,3490091,3490242,3490091,3490668,3490565,3490136,3490091,3490466,3490091,3490668,3490565,3490136,3490091,3490466,3490091,3490668,3490645,3490136,3490091,3490466,3490091,3490868,3490645,3490136,3490099,3490466,3490099,3490868,3490693,3490136,3490099,3490514,3490099,3490868,3490693,3490136,3490099,3490514,3490099,3490868,3490709,3490136,3490107,3490514,3490107,3490868,3490709,3490136,3490107,3490514,3490107,3490868,3491021,3490136,3490107,3490786,3490107,3490868,3491021,3490136,3490115,3490786,3490115,3490988,3490136,3490115,3490786,3490115,3490988,3490144,3490115,3490115,3490988,3490144,3490673,3490988,3490144,3490673,3490988,3490144,3490673,3490988,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490144,3490673,3490673,3490673,3490673,3490673,3490673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L10 W16/25; N=130; EHP=8452.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x4,fast:64x4,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x3,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L10 W16/25; N=130; EHP=18431.702922; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x6,normal:17x15,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3492136,3492673,3492242,3492019,3492668,3492253,3492136,3492673,3492242,3492019,3492668,3492253,3492136,3492673,3492242,3492019,3492668,3492325,3492136,3492673,3492242,3492091,3492668,3492325,3492136,3492673,3492466,3492091,3492668,3492565,3492136,3492673,3492466,3492091,3492668,3492565,3492136,3492673,3492466,3492099,3492668,3492645,3492136,3492673,3492466,3492099,3492868,3492645,3492136,3492673,3492514,3492099,3492868,3492693,3492136,3492673,3492514,3492107,3492868,3492693,3492136,3492673,3492514,3492107,3492868,3492709,3492136,3492673,3492514,3492107,3492868,3492709,3492136,3492673,3492786,3492115,3492868,3493021,3492136,3492673,3492786,3492115,3492988,3492136,3492673,3492786,3492115,3492988,3492136,3492673,3492786,3492115,3492988,3492136,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492673,3492673,3492673,3492673,3492673</t>
+          <t>3492136,3492019,3492242,3492019,3492668,3492253,3492136,3492019,3492242,3492019,3492668,3492253,3492136,3492019,3492242,3492019,3492668,3492325,3492136,3492091,3492242,3492091,3492668,3492325,3492136,3492091,3492466,3492091,3492668,3492565,3492136,3492091,3492466,3492091,3492668,3492565,3492136,3492099,3492466,3492099,3492668,3492645,3492136,3492099,3492466,3492099,3492868,3492645,3492136,3492099,3492514,3492099,3492868,3492693,3492136,3492107,3492514,3492107,3492868,3492693,3492136,3492107,3492514,3492107,3492868,3492709,3492136,3492107,3492514,3492107,3492868,3492709,3492136,3492115,3492786,3492115,3492868,3493021,3492136,3492115,3492786,3492115,3492988,3492136,3492115,3492786,3492115,3492988,3492136,3492115,3492786,3492115,3492988,3492136,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492988,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492144,3492673,3492673,3492673,3492673,3492673,3492673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L10 W17/25; N=136; EHP=8622.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L10 W17/25; N=136; EHP=18793.316312; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x16,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3494136,3494673,3494242,3494019,3494668,3494253,3494136,3494673,3494242,3494019,3494668,3494253,3494136,3494673,3494242,3494019,3494668,3494325,3494136,3494673,3494242,3494019,3494668,3494325,3494136,3494673,3494242,3494091,3494668,3494565,3494136,3494673,3494466,3494091,3494668,3494565,3494136,3494673,3494466,3494091,3494668,3494645,3494136,3494673,3494466,3494099,3494868,3494645,3494136,3494673,3494466,3494099,3494868,3494693,3494136,3494673,3494514,3494099,3494868,3494693,3494136,3494673,3494514,3494099,3494868,3494709,3494136,3494673,3494514,3494107,3494868,3494709,3494136,3494673,3494514,3494107,3494868,3495021,3494136,3494673,3494786,3494107,3494868,3495021,3494136,3494673,3494786,3494115,3494988,3494136,3494673,3494786,3494115,3494988,3494136,3494673,3494786,3494115,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494673,3494673,3494673,3494673,3494673</t>
+          <t>3494136,3494019,3494242,3494019,3494668,3494253,3494136,3494019,3494242,3494019,3494668,3494253,3494136,3494019,3494242,3494019,3494668,3494325,3494136,3494019,3494242,3494019,3494668,3494325,3494136,3494091,3494242,3494091,3494668,3494565,3494136,3494091,3494466,3494091,3494668,3494565,3494136,3494091,3494466,3494091,3494668,3494645,3494136,3494099,3494466,3494099,3494868,3494645,3494136,3494099,3494466,3494099,3494868,3494693,3494136,3494099,3494514,3494099,3494868,3494693,3494136,3494099,3494514,3494099,3494868,3494709,3494136,3494107,3494514,3494107,3494868,3494709,3494136,3494107,3494514,3494107,3494868,3495021,3494136,3494107,3494786,3494107,3494868,3495021,3494136,3494115,3494786,3494115,3494988,3494136,3494115,3494786,3494115,3494988,3494136,3494115,3494786,3494115,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494988,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494144,3494673,3494673,3494673,3494673,3494673,3494673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L10 W18/25; N=142; EHP=9213.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x17,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L10 W18/25; N=142; EHP=20084.511281; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3496136,3496673,3496242,3496019,3496668,3496253,3496136,3496673,3496242,3496019,3496668,3496253,3496136,3496673,3496242,3496019,3496668,3496325,3496136,3496673,3496242,3496019,3496668,3496325,3496136,3496673,3496466,3496091,3496668,3496565,3496136,3496673,3496466,3496091,3496668,3496565,3496136,3496673,3496466,3496091,3496668,3496645,3496136,3496673,3496466,3496091,3496868,3496645,3496136,3496673,3496514,3496099,3496868,3496693,3496136,3496673,3496514,3496099,3496868,3496693,3496136,3496673,3496514,3496099,3496868,3496709,3496136,3496673,3496514,3496107,3496868,3496709,3496136,3496673,3496786,3496107,3496868,3497021,3496136,3496673,3496786,3496107,3496868,3497021,3496136,3496673,3496786,3496107,3496868,3496136,3496673,3496786,3496115,3496988,3496136,3496673,3496786,3496115,3496988,3496136,3496673,3496115,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496673,3496673,3496673,3496673,3496673</t>
+          <t>3496136,3496019,3496242,3496019,3496668,3496253,3496136,3496019,3496242,3496019,3496668,3496253,3496136,3496019,3496242,3496019,3496668,3496325,3496136,3496019,3496242,3496019,3496668,3496325,3496136,3496091,3496466,3496091,3496668,3496565,3496136,3496091,3496466,3496091,3496668,3496565,3496136,3496091,3496466,3496091,3496668,3496645,3496136,3496091,3496466,3496091,3496868,3496645,3496136,3496099,3496514,3496099,3496868,3496693,3496136,3496099,3496514,3496099,3496868,3496693,3496136,3496099,3496514,3496099,3496868,3496709,3496136,3496107,3496514,3496107,3496868,3496709,3496136,3496107,3496786,3496107,3496868,3497021,3496136,3496107,3496786,3496107,3496868,3497021,3496136,3496107,3496786,3496107,3496868,3496136,3496115,3496786,3496115,3496988,3496136,3496115,3496786,3496115,3496988,3496136,3496115,3496115,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496988,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496144,3496673,3496673,3496673,3496673,3496673,3496673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L10 W19/25; N=148; EHP=10670.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x41,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L10 W19/25; N=148; EHP=23266.401717; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3498136,3498673,3498242,3498019,3498668,3498253,3498566,3498136,3498673,3498242,3498019,3498668,3498253,3498136,3498673,3498242,3498019,3498668,3498325,3498136,3498673,3498242,3498091,3498668,3498325,3498136,3498673,3498466,3498091,3498668,3498565,3498136,3498673,3498466,3498091,3498668,3498565,3498136,3498673,3498466,3498091,3498668,3498645,3498136,3498673,3498466,3498099,3498668,3498645,3498136,3498673,3498466,3498099,3498868,3498693,3498136,3498673,3498514,3498099,3498868,3498693,3498136,3498673,3498514,3498107,3498868,3498693,3498136,3498673,3498514,3498107,3498868,3498709,3498136,3498673,3498514,3498107,3498868,3498709,3498136,3498673,3498514,3498107,3498868,3499021,3498136,3498673,3498786,3498115,3498868,3499021,3498136,3498673,3498786,3498115,3498988,3498136,3498673,3498786,3498115,3498988,3498136,3498673,3498786,3498115,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498673,3498673,3498673,3498673,3498673,3498673,3498673</t>
+          <t>3498136,3498019,3498242,3498019,3498668,3498253,3498566,3498136,3498019,3498242,3498019,3498668,3498253,3498136,3498019,3498242,3498019,3498668,3498325,3498136,3498091,3498242,3498091,3498668,3498325,3498136,3498091,3498466,3498091,3498668,3498565,3498136,3498091,3498466,3498091,3498668,3498565,3498136,3498091,3498466,3498091,3498668,3498645,3498136,3498099,3498466,3498099,3498668,3498645,3498136,3498099,3498466,3498099,3498868,3498693,3498136,3498099,3498514,3498099,3498868,3498693,3498136,3498107,3498514,3498107,3498868,3498693,3498136,3498107,3498514,3498107,3498868,3498709,3498136,3498107,3498514,3498107,3498868,3498709,3498136,3498107,3498514,3498107,3498868,3499021,3498136,3498115,3498786,3498115,3498868,3499021,3498136,3498115,3498786,3498115,3498988,3498136,3498115,3498786,3498115,3498988,3498136,3498115,3498786,3498115,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498988,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498144,3498673,3498673,3498673,3498673,3498673,3498673,3498673,3498673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L10 W20/25; N=154; EHP=17918.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:70x1,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x3,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L10 W20/25; N=154; EHP=39041.049115; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:70x1,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x18,normal:18x18,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017406,10017416,10017408,10048560,10017415,10017409,10017406,10017416,10017408,10048560,10017415,10017409,10017406,10017416,10017408,10048560,10017415,10017409,10017406,10017416,10017408,10048560,10017415,10017410,10017406,10017416,10017408,10017403,10017415,10017410,10017406,10017416,10017411,10017403,10017415,10017410,10017406,10017416,10017411,10017403,10017415,10017413,10017406,10017416,10017411,10017403,10017415,10017413,10017406,10017416,10017411,10048561,10017419,10017414,10017406,10017416,10017412,10048561,10017419,10017414,10017406,10017416,10017412,10048561,10017419,10045162,10017406,10017416,10017412,10048561,10017419,10045162,10017406,10017416,10017412,10017404,10017419,10017417,10017406,10017416,10017412,10017404,10017419,10017417,10017406,10017416,10017418,10017404,10017419,10017421,10017406,10017416,10017418,10017405,10017419,10017421,10017406,10017416,10017418,10017405,10017420,10017406,10017416,10017418,10017405,10017420,10017406,10017416,10017418,10017405,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017416,10017416,10017416,10017416,10017416,10017416</t>
+          <t>10017406,10048560,10017408,10048560,10017415,10017409,10017406,10048560,10017408,10048560,10017415,10017409,10017406,10048560,10017408,10048560,10017415,10017409,10017406,10048560,10017408,10048560,10017415,10017410,10017406,10017403,10017408,10017403,10017415,10017410,10017406,10017403,10017411,10017403,10017415,10017410,10017406,10017403,10017411,10017403,10017415,10017413,10017406,10017403,10017411,10017403,10017415,10017413,10017406,10048561,10017411,10048561,10017419,10017414,10017406,10048561,10017412,10048561,10017419,10017414,10017406,10048561,10017412,10048561,10017419,10045162,10017406,10048561,10017412,10048561,10017419,10045162,10017406,10017404,10017412,10017404,10017419,10017417,10017406,10017404,10017412,10017404,10017419,10017417,10017406,10017404,10017418,10017404,10017419,10017421,10017406,10017405,10017418,10017405,10017419,10017421,10017406,10017405,10017418,10017405,10017420,10017406,10017405,10017418,10017405,10017420,10017406,10017405,10017418,10017405,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017420,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017407,10017416,10017416,10017416,10017416,10017416,10017416,10017416</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L10 W21/25; N=160; EHP=18277.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x3,heavy:40x3,fast:58x4,fast:64x5,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L10 W21/25; N=160; EHP=39838.940055; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x3,heavy:40x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017425,10017434,10017427,10048562,10017433,10045163,10017425,10017434,10017427,10048562,10017433,10045163,10017425,10017434,10017427,10048562,10017433,10017428,10017425,10017434,10017427,10048562,10017433,10017428,10017425,10017434,10017427,10017422,10017433,10017428,10017425,10017434,10017429,10017422,10017433,10017431,10017425,10017434,10017429,10017422,10017433,10017431,10017425,10017434,10017429,10017422,10017433,10017432,10017425,10017434,10017429,10048563,10017438,10017432,10017425,10017434,10017429,10048563,10017438,10017435,10017425,10017434,10017430,10048563,10017438,10017435,10017425,10017434,10017430,10048563,10017438,10017436,10017425,10017434,10017430,10017423,10017438,10017436,10017425,10017434,10017430,10017423,10017438,10017440,10017425,10017434,10017437,10017423,10017438,10017440,10017425,10017434,10017437,10017423,10017438,10017440,10017425,10017434,10017437,10017424,10017439,10017425,10017434,10017437,10017424,10017439,10017425,10017434,10017437,10017424,10017439,10017425,10017434,10017424,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017434,10017434,10017434,10017434,10017434</t>
+          <t>10017425,10048562,10017427,10048562,10017433,10045163,10017425,10048562,10017427,10048562,10017433,10045163,10017425,10048562,10017427,10048562,10017433,10017428,10017425,10048562,10017427,10048562,10017433,10017428,10017425,10017422,10017427,10017422,10017433,10017428,10017425,10017422,10017429,10017422,10017433,10017431,10017425,10017422,10017429,10017422,10017433,10017431,10017425,10017422,10017429,10017422,10017433,10017432,10017425,10048563,10017429,10048563,10017438,10017432,10017425,10048563,10017429,10048563,10017438,10017435,10017425,10048563,10017430,10048563,10017438,10017435,10017425,10048563,10017430,10048563,10017438,10017436,10017425,10017423,10017430,10017423,10017438,10017436,10017425,10017423,10017430,10017423,10017438,10017440,10017425,10017423,10017437,10017423,10017438,10017440,10017425,10017423,10017437,10017423,10017438,10017440,10017425,10017424,10017437,10017424,10017439,10017425,10017424,10017437,10017424,10017439,10017425,10017424,10017437,10017424,10017439,10017425,10017424,10017424,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017439,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017426,10017434,10017434,10017434,10017434,10017434,10017434</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L10 W22/25; N=166; EHP=18643.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x3,fast:58x5,fast:64x4,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x3</t>
+          <t>L10 W22/25; N=166; EHP=40647.477173; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x21,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017444,10017454,10017446,10048564,10017453,10017447,10017444,10017454,10017446,10048564,10017453,10017447,10017444,10017454,10017446,10048564,10017453,10017448,10017444,10017454,10017446,10048564,10017453,10017448,10017444,10017454,10017446,10017441,10017453,10017451,10017444,10017454,10017449,10017441,10017453,10017451,10017444,10017454,10017449,10017441,10017453,10017451,10017444,10017454,10017449,10017441,10017453,10017452,10017444,10017454,10017449,10048565,10017453,10017452,10017444,10017454,10017449,10048565,10017458,10017455,10017444,10017454,10017450,10048565,10017458,10017455,10017444,10017454,10017450,10048565,10017458,10017456,10017444,10017454,10017450,10048565,10017458,10017456,10017444,10017454,10017450,10017442,10017458,10017456,10017444,10017454,10017450,10017442,10017458,10017460,10017444,10017454,10017457,10017442,10017458,10017460,10017444,10017454,10017457,10017442,10017458,10017460,10017444,10017454,10017457,10017443,10017459,10017444,10017454,10017457,10017443,10017459,10017444,10017454,10017457,10017443,10017459,10017444,10017454,10017443,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017454,10017454,10017454,10017454,10017454,10017454,10017454</t>
+          <t>10017444,10048564,10017446,10048564,10017453,10017447,10017444,10048564,10017446,10048564,10017453,10017447,10017444,10048564,10017446,10048564,10017453,10017448,10017444,10048564,10017446,10048564,10017453,10017448,10017444,10017441,10017446,10017441,10017453,10017451,10017444,10017441,10017449,10017441,10017453,10017451,10017444,10017441,10017449,10017441,10017453,10017451,10017444,10017441,10017449,10017441,10017453,10017452,10017444,10048565,10017449,10048565,10017453,10017452,10017444,10048565,10017449,10048565,10017458,10017455,10017444,10048565,10017450,10048565,10017458,10017455,10017444,10048565,10017450,10048565,10017458,10017456,10017444,10048565,10017450,10048565,10017458,10017456,10017444,10017442,10017450,10017442,10017458,10017456,10017444,10017442,10017450,10017442,10017458,10017460,10017444,10017442,10017457,10017442,10017458,10017460,10017444,10017442,10017457,10017442,10017458,10017460,10017444,10017443,10017457,10017443,10017459,10017444,10017443,10017457,10017443,10017459,10017444,10017443,10017457,10017443,10017459,10017444,10017443,10017443,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017459,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017445,10017454,10017454,10017454,10017454,10017454,10017454,10017454,10017454</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L10 W23/25; N=172; EHP=19016.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x2,heavy:88x3,fast:98x5,medium:108x8,medium:123x8,heavy:127x3</t>
+          <t>L10 W23/25; N=172; EHP=41466.342040; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x9,medium:108x8,medium:123x8,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017464,10017474,10017466,10048566,10017473,10017467,10017464,10017474,10017466,10048566,10017473,10017467,10017464,10017474,10017466,10048566,10017473,10017468,10017464,10017474,10017466,10048566,10017473,10017468,10017464,10017474,10017466,10048566,10017473,10017471,10017464,10017474,10017469,10017461,10017473,10017471,10017464,10017474,10017469,10017461,10017473,10017471,10017464,10017474,10017469,10017461,10017473,10017472,10017464,10017474,10017469,10017461,10017478,10017472,10017464,10017474,10017469,10048567,10017478,10017472,10017464,10017474,10017469,10048567,10017478,10017475,10017464,10017474,10017470,10048567,10017478,10017475,10017464,10017474,10017470,10048567,10017478,10017476,10017464,10017474,10017470,10017462,10017478,10017476,10017464,10017474,10017470,10017462,10017478,10017476,10017464,10017474,10017470,10017462,10017478,10017480,10017464,10017474,10017477,10017462,10017478,10017480,10017464,10017474,10017477,10017463,10017479,10017464,10017474,10017477,10017463,10017479,10017464,10017474,10017477,10017463,10017479,10017464,10017474,10017477,10017463,10017479,10017464,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017474,10017474,10017474,10017474,10017474</t>
+          <t>10017464,10048566,10017466,10048566,10017473,10017467,10017464,10048566,10017466,10048566,10017473,10017467,10017464,10048566,10017466,10048566,10017473,10017468,10017464,10048566,10017466,10048566,10017473,10017468,10017464,10048566,10017466,10048566,10017473,10017471,10017464,10017461,10017469,10017461,10017473,10017471,10017464,10017461,10017469,10017461,10017473,10017471,10017464,10017461,10017469,10017461,10017473,10017472,10017464,10017461,10017469,10017461,10017478,10017472,10017464,10048567,10017469,10048567,10017478,10017472,10017464,10048567,10017469,10048567,10017478,10017475,10017464,10048567,10017470,10048567,10017478,10017475,10017464,10048567,10017470,10048567,10017478,10017476,10017464,10017462,10017470,10017462,10017478,10017476,10017464,10017462,10017470,10017462,10017478,10017476,10017464,10017462,10017470,10017462,10017478,10017480,10017464,10017462,10017477,10017462,10017478,10017480,10017464,10017463,10017477,10017463,10017479,10017464,10017463,10017477,10017463,10017479,10017464,10017463,10017477,10017463,10017479,10017464,10017463,10017477,10017463,10017479,10017464,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017479,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017465,10017474,10017474,10017474,10017474,10017474,10017474</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L10 W24/25; N=178; EHP=20362.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:70x3,heavy:80x3,medium:83x8,swarm:84x49,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L10 W24/25; N=178; EHP=44384.111849; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:70x3,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x8,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017484,10017494,10017486,10048568,10017493,10017487,10017499,10017484,10017494,10017486,10048568,10017493,10017487,10017484,10017494,10017486,10048568,10017493,10017487,10017484,10017494,10017486,10048568,10017493,10017488,10017484,10017494,10017486,10017481,10017493,10017488,10017484,10017494,10017486,10017481,10017493,10017491,10017484,10017494,10017489,10017481,10017493,10017491,10017484,10017494,10017489,10017481,10017493,10017492,10017484,10017494,10017489,10017481,10017493,10017492,10017484,10017494,10017489,10048569,10017498,10017492,10017484,10017494,10017489,10048569,10017498,10017495,10017484,10017494,10017490,10048569,10017498,10017495,10017484,10017494,10017490,10048569,10017498,10017495,10017484,10017494,10017490,10017482,10017498,10017496,10017484,10017494,10017490,10017482,10017498,10017496,10017484,10017494,10017490,10017482,10017498,10017496,10017484,10017494,10017490,10017482,10017498,10017501,10017484,10017494,10017497,10017482,10017498,10017501,10017484,10017494,10017497,10017483,10017500,10017484,10017494,10017497,10017483,10017500,10017484,10017494,10017497,10017483,10017500,10017484,10017494,10017497,10017483,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017494,10017494,10017494,10017494,10017494,10017494,10017494,10017494</t>
+          <t>10017484,10048568,10017486,10048568,10017493,10017487,10017499,10017484,10048568,10017486,10048568,10017493,10017487,10017484,10048568,10017486,10048568,10017493,10017487,10017484,10048568,10017486,10048568,10017493,10017488,10017484,10017481,10017486,10017481,10017493,10017488,10017484,10017481,10017486,10017481,10017493,10017491,10017484,10017481,10017489,10017481,10017493,10017491,10017484,10017481,10017489,10017481,10017493,10017492,10017484,10017481,10017489,10017481,10017493,10017492,10017484,10048569,10017489,10048569,10017498,10017492,10017484,10048569,10017489,10048569,10017498,10017495,10017484,10048569,10017490,10048569,10017498,10017495,10017484,10048569,10017490,10048569,10017498,10017495,10017484,10017482,10017490,10017482,10017498,10017496,10017484,10017482,10017490,10017482,10017498,10017496,10017484,10017482,10017490,10017482,10017498,10017496,10017484,10017482,10017490,10017482,10017498,10017501,10017484,10017482,10017497,10017482,10017498,10017501,10017484,10017483,10017497,10017483,10017500,10017484,10017483,10017497,10017483,10017500,10017484,10017483,10017497,10017483,10017500,10017484,10017483,10017497,10017483,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017500,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017485,10017494,10017494,10017494,10017494,10017494,10017494,10017494,10017494,10017494</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L10 W25/25; N=184; EHP=40645.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x21,fast:30x6,heavy:31x3,heavy:40x2,fast:58x5,fast:64x6,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x51,heavy:86x3,heavy:88x3,fast:98x5,medium:108x9,elite:123x1,medium:123x9,heavy:127x2</t>
+          <t>L10 W25/25; N=184; EHP=88588.353652; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x21,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L10/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L10/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>262</v>
+        <v>320</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>241</v>
+        <v>340</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>213</v>
+        <v>340</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>185</v>
+        <v>290</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>171</v>
+        <v>340</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>157</v>
+        <v>280</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>143</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
